--- a/public/assets/excel/ot_plans.xlsx
+++ b/public/assets/excel/ot_plans.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo LOQ\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Asus\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF2866BB-FBFC-4F99-B712-17FECDE44315}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{038C2D48-0D80-4796-8A2C-121D8E692A9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="34">
   <si>
     <t>Name</t>
   </si>
@@ -52,9 +52,6 @@
     <t>Overtime_End_Time</t>
   </si>
   <si>
-    <t>Active_Ind</t>
-  </si>
-  <si>
     <t>Regular OT</t>
   </si>
   <si>
@@ -97,27 +94,6 @@
     <t>night</t>
   </si>
   <si>
-    <t>18:00</t>
-  </si>
-  <si>
-    <t>09:00</t>
-  </si>
-  <si>
-    <t>08:00</t>
-  </si>
-  <si>
-    <t>22:00</t>
-  </si>
-  <si>
-    <t>17:00</t>
-  </si>
-  <si>
-    <t>04:00</t>
-  </si>
-  <si>
-    <t>23:00</t>
-  </si>
-  <si>
     <t>active</t>
   </si>
   <si>
@@ -137,6 +113,15 @@
   </si>
   <si>
     <t>other</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>10.15 AM</t>
+  </si>
+  <si>
+    <t>4.00 PM</t>
   </si>
 </sst>
 </file>
@@ -195,11 +180,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -218,9 +207,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -258,9 +247,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -293,26 +282,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -345,26 +317,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -539,23 +494,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12.77734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.5546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.08984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.90625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.54296875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.81640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="18" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="21.21875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="21.1796875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="24" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="24.33203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="19" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="18.109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="24.36328125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="19" style="3" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18.08984375" style="3" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -572,7 +527,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>5</v>
@@ -583,31 +538,31 @@
       <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="2" t="s">
         <v>9</v>
       </c>
       <c r="L1" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>11</v>
-      </c>
       <c r="B2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="E2" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="H2">
         <v>1</v>
@@ -615,31 +570,31 @@
       <c r="I2">
         <v>4</v>
       </c>
-      <c r="J2" t="s">
-        <v>25</v>
-      </c>
-      <c r="K2" t="s">
+      <c r="J2" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="L2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E3" t="s">
         <v>28</v>
-      </c>
-      <c r="L2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D3" t="s">
-        <v>34</v>
-      </c>
-      <c r="E3" t="s">
-        <v>36</v>
       </c>
       <c r="F3">
         <v>2</v>
@@ -650,31 +605,31 @@
       <c r="I3">
         <v>8</v>
       </c>
-      <c r="J3" t="s">
+      <c r="J3" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="L3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4" t="s">
         <v>26</v>
       </c>
-      <c r="K3" t="s">
-        <v>29</v>
-      </c>
-      <c r="L3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D4" t="s">
-        <v>34</v>
-      </c>
       <c r="E4" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="G4">
         <v>250</v>
@@ -685,31 +640,31 @@
       <c r="I4">
         <v>10</v>
       </c>
-      <c r="J4" t="s">
+      <c r="J4" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="L4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E5" t="s">
         <v>27</v>
-      </c>
-      <c r="K4" t="s">
-        <v>25</v>
-      </c>
-      <c r="L4" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" t="s">
-        <v>19</v>
-      </c>
-      <c r="C5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D5" t="s">
-        <v>34</v>
-      </c>
-      <c r="E5" t="s">
-        <v>35</v>
       </c>
       <c r="H5">
         <v>1.5</v>
@@ -717,31 +672,31 @@
       <c r="I5">
         <v>6</v>
       </c>
-      <c r="J5" t="s">
+      <c r="J5" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="L5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" t="s">
         <v>28</v>
-      </c>
-      <c r="K5" t="s">
-        <v>30</v>
-      </c>
-      <c r="L5" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" t="s">
-        <v>38</v>
-      </c>
-      <c r="D6" t="s">
-        <v>33</v>
-      </c>
-      <c r="E6" t="s">
-        <v>36</v>
       </c>
       <c r="F6">
         <v>1.5</v>
@@ -755,14 +710,14 @@
       <c r="I6">
         <v>5</v>
       </c>
-      <c r="J6" t="s">
-        <v>25</v>
-      </c>
-      <c r="K6" t="s">
-        <v>31</v>
+      <c r="J6" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="L6" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/public/assets/excel/ot_plans.xlsx
+++ b/public/assets/excel/ot_plans.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\hrms\public\assets\csv\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CCC81EE8-99B1-4FB9-A2D8-427F61DB12DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{705AEEE3-BBC6-468B-9D73-F046C1104AED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{0CFE3684-D380-4965-BF50-73AA526BC3D1}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{98BDCDA1-9A16-4958-9130-6EDB9F656944}"/>
   </bookViews>
   <sheets>
     <sheet name="ot_plans" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
     <t>Custom_Overtime_Rate</t>
   </si>
   <si>
-    <t>Maximum_Overtime_Hours</t>
+    <t>Maximum_Overtime_(minutes)</t>
   </si>
   <si>
     <t>Status</t>
@@ -948,7 +948,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC6E4BC5-6BC8-479D-870E-FFD464E8C3BE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B195C7B-681C-42AB-8245-140F0544F433}">
   <dimension ref="A1:H6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
